--- a/docs/03_backlog.xlsx
+++ b/docs/03_backlog.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="600" windowWidth="27040" windowHeight="15320" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Backlog" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Epics" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Legend" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Backlog" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Epics" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Legend" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Backlog'!$A$1:$I$75</definedName>
@@ -486,7 +486,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I139"/>
+  <dimension ref="A1:I146"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -7118,6 +7118,365 @@
         </is>
       </c>
     </row>
+    <row r="140" ht="112" customHeight="1">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>US-123</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>20. Survey Data Hub Completion &amp; Separation</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>DIH (ING) / Survey Data Hub</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>NSR MIS Architecture Team</t>
+        </is>
+      </c>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>As the NSR MIS Architecture Team, I want the Survey Data Hub/DIH boundary and its versioned NSR exchange contract defined and deployed independently, so that survey-source churn cannot write directly into the registry.</t>
+        </is>
+      </c>
+      <c r="F140" t="inlineStr">
+        <is>
+          <t>- ADR defines ownership, trust boundary, service identity, network policy, retention, and failure handling
+- Hub has its own deployable process and logical database with no direct writes to registry domain tables
+- Authenticated versioned internal API accepts only approved exchange records
+- OpenAPI + contract tests cover idempotency key, Hub/source IDs, form and mapping versions, and approval timestamp
+- Contract has an explicit version/deprecation policy</t>
+        </is>
+      </c>
+      <c r="G140" t="inlineStr">
+        <is>
+          <t>Must</t>
+        </is>
+      </c>
+      <c r="H140" t="inlineStr">
+        <is>
+          <t>Survey Data Hub Build Specification (22 Sep 2026); ADR-0001/0007/0009/0034</t>
+        </is>
+      </c>
+      <c r="I140" t="inlineStr">
+        <is>
+          <t>Foundation; blocks all production Hub promotion.</t>
+        </is>
+      </c>
+    </row>
+    <row r="141" ht="112" customHeight="1">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>US-124</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>20. Survey Data Hub Completion &amp; Separation</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>DIH (ING) / Survey Data Hub</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>Source Admin</t>
+        </is>
+      </c>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>As a Source Admin, I want every Kobo submission and attachment preserved as an immutable, integrity-checked source record, so that collection history remains auditable despite later review or questionnaire changes.</t>
+        </is>
+      </c>
+      <c r="F141" t="inlineStr">
+        <is>
+          <t>- Preserve Kobo project/asset/form/submission IDs, timestamps, enumerator, device, round, form version/hash, payload, and deleted status
+- Idempotent replay on Kobo source identity
+- Cryptographic source hash; encrypted raw/attachment archive and separate metadata
+- Database-level append-only control, with only a documented retention/archive exception
+- Restricted, audited access to raw PII, GPS, NINs, and attachments</t>
+        </is>
+      </c>
+      <c r="G141" t="inlineStr">
+        <is>
+          <t>Must</t>
+        </is>
+      </c>
+      <c r="H141" t="inlineStr">
+        <is>
+          <t>Survey Data Hub Build Specification (22 Sep 2026); ADR-0001/0007/0009/0034</t>
+        </is>
+      </c>
+      <c r="I141" t="inlineStr">
+        <is>
+          <t>Extends RawLanding; does not mutate historical payloads.</t>
+        </is>
+      </c>
+    </row>
+    <row r="142" ht="112" customHeight="1">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>US-125</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>20. Survey Data Hub Completion &amp; Separation</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>DIH (ING) / Survey Data Hub</t>
+        </is>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>Data Manager</t>
+        </is>
+      </c>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>As a Data Manager, I want Kobo forms, archived definitions, versions, and survey rounds governed alongside FormVersion, so that historical submissions render and validate against their real questionnaire.</t>
+        </is>
+      </c>
+      <c r="F142" t="inlineStr">
+        <is>
+          <t>- Link Kobo project/form to survey round and existing FormVersion
+- Govern effective dates, form hash, archived XLSForm/definition, release notes, author, and approver
+- Resolve unreliable source versions by deterministic hash/effective-date rule and record rationale
+- Never treat renamed/materially re-coded questions as equivalent without approved version/mapping change
+- Multiple versions coexist in search, validation, and viewer rendering</t>
+        </is>
+      </c>
+      <c r="G142" t="inlineStr">
+        <is>
+          <t>Must</t>
+        </is>
+      </c>
+      <c r="H142" t="inlineStr">
+        <is>
+          <t>Survey Data Hub Build Specification (22 Sep 2026); ADR-0001/0007/0009/0034</t>
+        </is>
+      </c>
+      <c r="I142" t="inlineStr">
+        <is>
+          <t>Builds on US-117..120 and ADR-0034.</t>
+        </is>
+      </c>
+    </row>
+    <row r="143" ht="112" customHeight="1">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>US-126</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>20. Survey Data Hub Completion &amp; Separation</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>DIH (ING) / Survey Data Hub</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>Data-quality Reviewer</t>
+        </is>
+      </c>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>As a Data-quality Reviewer, I want configurable, form-aware validation issues and duplicate signals in an assigned review workflow, so that I can resolve, reject, or document exceptions without changing source records.</t>
+        </is>
+      </c>
+      <c r="F143" t="inlineStr">
+        <is>
+          <t>- Reuse shared DQA/DDUP logic; do not fork it in the Hub
+- Validation issues include rule/version, severity, field path, message, status, reviewer, and resolution note
+- Audited lifecycle: open, in review, resolved, approved exception, rejected
+- Rules support form/version, round, geography, and source scope
+- Only the approval role may approve; staged editor cannot self-approve</t>
+        </is>
+      </c>
+      <c r="G143" t="inlineStr">
+        <is>
+          <t>Must</t>
+        </is>
+      </c>
+      <c r="H143" t="inlineStr">
+        <is>
+          <t>Survey Data Hub Build Specification (22 Sep 2026); ADR-0001/0007/0009/0034</t>
+        </is>
+      </c>
+      <c r="I143" t="inlineStr">
+        <is>
+          <t>Adds issue/review workflow above existing DQA results and DDUP candidates.</t>
+        </is>
+      </c>
+    </row>
+    <row r="144" ht="112" customHeight="1">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>US-127</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>20. Survey Data Hub Completion &amp; Separation</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>DIH (ING) / Survey Data Hub</t>
+        </is>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>Data-quality Reviewer</t>
+        </is>
+      </c>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>As an authorized Hub user, I want a form-aware submission viewer and review queue, so that I can safely find, assess, and act on survey records across questionnaire versions.</t>
+        </is>
+      </c>
+      <c r="F144" t="inlineStr">
+        <is>
+          <t>- Django admin remains the audit-safe fallback while a production console is delivered
+- Scoped search/filter by identifiers, PII search keys, enumerator, date, geography, round, form version, state, and severity
+- Viewer shows historical labels, repeats, permitted attachments, map/GPS, raw audit view, review history, and sync outcome
+- Analyst view is de-identified by default; sensitive reads and actions are audited
+- Reviewer actions remain separate from raw source records</t>
+        </is>
+      </c>
+      <c r="G144" t="inlineStr">
+        <is>
+          <t>Must</t>
+        </is>
+      </c>
+      <c r="H144" t="inlineStr">
+        <is>
+          <t>Survey Data Hub Build Specification (22 Sep 2026); ADR-0001/0007/0009/0034</t>
+        </is>
+      </c>
+      <c r="I144" t="inlineStr">
+        <is>
+          <t>Current JSX console is a design harness, not the production UI.</t>
+        </is>
+      </c>
+    </row>
+    <row r="145" ht="112" customHeight="1">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>US-128</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>20. Survey Data Hub Completion &amp; Separation</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>DIH (ING) / Survey Data Hub</t>
+        </is>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>Data Manager / NSR MIS Integration Account</t>
+        </is>
+      </c>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t>As a Data Manager, I want approved survey records transformed through an independently versioned NSR exchange mapping and synchronized idempotently, so that source-form changes cannot corrupt the registry.</t>
+        </is>
+      </c>
+      <c r="F145" t="inlineStr">
+        <is>
+          <t>- Separate inbound source-to-canonical mappings from approved canonical-to-NSR exchange mappings
+- Outbound mappings record source path, target, transform, code translation, requiredness, version, author, and approver
+- Changed question names/codes require a new approved mapping
+- Only approved records create export events
+- Persist safe request metadata, returned NSR IDs, retries, protected errors, and reconciliation state
+- Temporary failures use bounded retry; uncertain/permanent failures enter manual reconciliation</t>
+        </is>
+      </c>
+      <c r="G145" t="inlineStr">
+        <is>
+          <t>Must</t>
+        </is>
+      </c>
+      <c r="H145" t="inlineStr">
+        <is>
+          <t>Survey Data Hub Build Specification (22 Sep 2026); ADR-0001/0007/0009/0034</t>
+        </is>
+      </c>
+      <c r="I145" t="inlineStr">
+        <is>
+          <t>Replaces direct in-process promotion with controlled exchange.</t>
+        </is>
+      </c>
+    </row>
+    <row r="146" ht="112" customHeight="1">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>US-129</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>20. Survey Data Hub Completion &amp; Separation</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>DIH (ING) / Survey Data Hub</t>
+        </is>
+      </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>System Administrator / DPO</t>
+        </is>
+      </c>
+      <c r="E146" t="inlineStr">
+        <is>
+          <t>As a System Administrator and DPO, I want monitoring, retention, recovery, and pilot controls for the Hub, so that Kobo collection can be introduced without creating an unmanaged shadow registry.</t>
+        </is>
+      </c>
+      <c r="F146" t="inlineStr">
+        <is>
+          <t>- Monitor polling/webhooks, ingestion and synchronization failures, and reconciliation
+- Version backup, restore, retention, legal-hold, and incident-response runbooks
+- Enforce Hub roles at API/UI layers
+- Load/recovery test 100,000 submissions and replay idempotency
+- Pilot sequence: archive-only, reviewer-only, limited approved cohort, reconciliation
+- DPO/access-review/deployment sign-off is a production promotion gate</t>
+        </is>
+      </c>
+      <c r="G146" t="inlineStr">
+        <is>
+          <t>Should</t>
+        </is>
+      </c>
+      <c r="H146" t="inlineStr">
+        <is>
+          <t>Survey Data Hub Build Specification (22 Sep 2026); ADR-0001/0007/0009/0034</t>
+        </is>
+      </c>
+      <c r="I146" t="inlineStr">
+        <is>
+          <t>Pilot-readiness gate; depends on US-123..128.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:I75"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -7130,7 +7489,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F20"/>
+  <dimension ref="A1:F21"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -7624,6 +7983,30 @@
         <v>1</v>
       </c>
       <c r="F20" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" ht="30" customHeight="1">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>20. Survey Data Hub Completion &amp; Separation</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>DIH (ING) / Survey Data Hub</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>7</v>
+      </c>
+      <c r="D21" t="n">
+        <v>6</v>
+      </c>
+      <c r="E21" t="n">
+        <v>1</v>
+      </c>
+      <c r="F21" t="n">
         <v>0</v>
       </c>
     </row>

--- a/docs/03_backlog.xlsx
+++ b/docs/03_backlog.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="600" windowWidth="27040" windowHeight="15320" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Backlog" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Epics" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Legend" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Backlog" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Epics" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Legend" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Backlog'!$A$1:$I$75</definedName>
@@ -486,7 +486,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I146"/>
+  <dimension ref="A1:I148"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -7474,6 +7474,110 @@
       <c r="I146" t="inlineStr">
         <is>
           <t>Pilot-readiness gate; depends on US-123..128.</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>US-130</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>16. Data Integration Hub</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>DIH (ING) / SEC</t>
+        </is>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>Data Protection Officer</t>
+        </is>
+      </c>
+      <c r="E147" t="inlineStr">
+        <is>
+          <t>As the Data Protection Officer, I want a stated, enforced retention period for rejected and quarantined staging records, so that personal data refused entry to the registry is not kept indefinitely without a lawful basis.</t>
+        </is>
+      </c>
+      <c r="F147" t="inlineStr">
+        <is>
+          <t>- Retention period defined per terminal state and recorded in an ADR with DPO sign-off
+- Scheduled disposal job; audit chain, PromotionDecision and voided provisional ID survive disposal
+- Payload cleared irreversibly and the disposal itself audited
+- Legal-hold flag exempts a record, auditable
+- Dry-run reports what a run would dispose of; first production run is a dry run
+- Policy covers records already past the period on the day it ships</t>
+        </is>
+      </c>
+      <c r="G147" t="inlineStr">
+        <is>
+          <t>Must</t>
+        </is>
+      </c>
+      <c r="H147" t="inlineStr">
+        <is>
+          <t>Production review 22 Sep 2026; SAD §4.6 (AC-DIH-REJECT-VOID); DPPA 2019</t>
+        </is>
+      </c>
+      <c r="I147" t="inlineStr">
+        <is>
+          <t>See docs/stories/US-130-131_rejected_record_lifecycle.md. 15 rejected records on production retain full payloads incl. NIN hashes and GPS. The only retention job in the module is a comment. Period is a DPO decision — do not default it.</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>US-131</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>16. Data Integration Hub</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>DIH (ING) / GRM</t>
+        </is>
+      </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>Household respondent / Source Admin</t>
+        </is>
+      </c>
+      <c r="E148" t="inlineStr">
+        <is>
+          <t>As a household whose registration was refused, I want to be told that it was refused and why, so that I can correct the record or raise a grievance instead of waiting for an outcome that will never come.</t>
+        </is>
+      </c>
+      <c r="F148" t="inlineStr">
+        <is>
+          <t>- Rejection queues a notification to the household contact number of record (ADR-0033) or the source system owner
+- Message carries the reason and the grievance route, never a NIN or provisional ID
+- Bulk vs case-by-case rejections have explicit, separate notification policy
+- Absence of a contact number is recorded and visible on the Rejected tab
+- Delivery success/failure auditable, retried under a stated policy, surfaced on final failure
+- Transactional-messaging consent respected per ADR-0031</t>
+        </is>
+      </c>
+      <c r="G148" t="inlineStr">
+        <is>
+          <t>Must</t>
+        </is>
+      </c>
+      <c r="H148" t="inlineStr">
+        <is>
+          <t>Production review 22 Sep 2026; SAD §4.6 (AC-DIH-REJECT-VOID); DPPA 2019</t>
+        </is>
+      </c>
+      <c r="I148" t="inlineStr">
+        <is>
+          <t>See docs/stories/US-130-131_rejected_record_lifecycle.md. reject_stage_record's docstring states the requirement and its absence: the path was never built. GRM must accept a grievance referencing a record with no registry entry.</t>
         </is>
       </c>
     </row>
@@ -7902,10 +8006,10 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="D17" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="E17" t="n">
         <v>1</v>

--- a/docs/03_backlog.xlsx
+++ b/docs/03_backlog.xlsx
@@ -1,17 +1,17 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="600" windowWidth="27040" windowHeight="15320" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Backlog" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Epics" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Legend" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Backlog" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Epics" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Legend" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Backlog'!$A$1:$I$75</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Backlog'!$A$1:$I$150</definedName>
   </definedNames>
   <calcPr calcId="0" fullCalcOnLoad="1"/>
 </workbook>
@@ -486,7 +486,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I148"/>
+  <dimension ref="A1:I150"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -7581,8 +7581,112 @@
         </is>
       </c>
     </row>
+    <row r="149" ht="112" customHeight="1">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>US-149</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>15. Deduplication &amp; Record Matching</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>DAT-DDUP</t>
+        </is>
+      </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>System Admin / DQA Approver</t>
+        </is>
+      </c>
+      <c r="E149" t="inlineStr">
+        <is>
+          <t>As a System Administrator, I want a governed Tier 2 exact-phone matching model, so that normalised phone matches can be reviewed without code-defined matching policy.</t>
+        </is>
+      </c>
+      <c r="F149" t="inlineStr">
+        <is>
+          <t>- Uses the canonical derived field telephone_1_e164 and the approved DDUP configuration only
+- No comparison field, score, queue threshold, or matching reason is supplied by application code
+- Draft model validates against the Questionnaire/Data Dictionary and derived-field registry before submission
+- A different authorised approver activates the version; the preceding active version is retained and auditable
+- Discovery, DIH candidate screening, and the DDUP queue consume the same approved model version
+- Regression tests cover disabled, valid, unregistered-field, and approval-separation cases</t>
+        </is>
+      </c>
+      <c r="G149" t="inlineStr">
+        <is>
+          <t>Should</t>
+        </is>
+      </c>
+      <c r="H149" t="inlineStr">
+        <is>
+          <t>DDUP configuration SSOT; Questionnaire Authoring Data Dictionary; ADR-0001</t>
+        </is>
+      </c>
+      <c r="I149" t="inlineStr">
+        <is>
+          <t>Blocked until the phone-normalisation contract and policy values are approved. Tier 2 must begin disabled; do not introduce code defaults.</t>
+        </is>
+      </c>
+    </row>
+    <row r="150" ht="112" customHeight="1">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>US-150</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>15. Deduplication &amp; Record Matching</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>DAT-DDUP</t>
+        </is>
+      </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>System Admin / DQA Approver / DPO</t>
+        </is>
+      </c>
+      <c r="E150" t="inlineStr">
+        <is>
+          <t>As a System Administrator and DPO, I want a governed Tier 3 probabilistic matching model, so that calibrated candidate matching can be introduced only through an approved, auditable model version.</t>
+        </is>
+      </c>
+      <c r="F150" t="inlineStr">
+        <is>
+          <t>- Features, comparators, weights, blocking field, review threshold, and any auto-merge policy come solely from the approved DDUP configuration
+- Every configured field must resolve through the Questionnaire/Data Dictionary or declared derived-field registry
+- Calibration evidence, DPO review, and independent approval are recorded before activation
+- Disabled or incomplete Tier 3 configuration produces no candidates; there is no fallback score, threshold, or weight in application code
+- Queue results retain model version and feature trace for review and reproducibility
+- Regression tests cover schema validation, calibration boundaries from configuration, approval separation, and DIH/DDUP shared-model propagation</t>
+        </is>
+      </c>
+      <c r="G150" t="inlineStr">
+        <is>
+          <t>Should</t>
+        </is>
+      </c>
+      <c r="H150" t="inlineStr">
+        <is>
+          <t>DDUP configuration SSOT; Questionnaire Authoring Data Dictionary; PMT/DQA/DIH integration; DPPA 2019</t>
+        </is>
+      </c>
+      <c r="I150" t="inlineStr">
+        <is>
+          <t>Blocked until comparison-comparator registry, calibration dataset, governance policy, and DPO approval exist. No auto-merge policy may be inferred.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:I75"/>
+  <autoFilter ref="A1:I150"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -7982,13 +8086,13 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D16" t="n">
         <v>5</v>
       </c>
       <c r="E16" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F16" t="n">
         <v>0</v>

--- a/docs/03_backlog.xlsx
+++ b/docs/03_backlog.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="600" windowWidth="27040" windowHeight="15320" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Backlog" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Epics" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Legend" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Backlog" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Epics" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Legend" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Backlog'!$A$1:$I$150</definedName>
@@ -7671,7 +7671,7 @@
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Should</t>
+          <t>Must</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
@@ -7681,7 +7681,7 @@
       </c>
       <c r="I150" t="inlineStr">
         <is>
-          <t>Blocked until comparison-comparator registry, calibration dataset, governance policy, and DPO approval exist. No auto-merge policy may be inferred.</t>
+          <t>LIVE TRIGGER (25 Sep 2026): Tier 3 is DISABLED in production. DdupModelVersion v2 was activated to end an outage and restores tier 1 only. Tier 3 had been running on unapproved code defaults in services.py (surname .30, first_name .30, date_of_birth .15, sex .10, village .15; threshold .85), which is precisely what this story forbids, so they were not carried into the approved model. While it is off, no new probabilistic pairs are found; the 17 pending tier-3 pairs already queued are untouched. Blockers partly cleared: the DDUP configuration contract (apps/ddup/config.py) and the comparator registry now exist, and `manage.py propose_tier3_weights` authors a DRAFT proposal (surname .35, first_name .35, date_of_birth .20, sex .10; village removed because tier 3 blocks BY village, so it scored 1.0 for every pair compared). Still needed: the calibration dataset, the governance policy and DPO approval. No auto-merge policy may be inferred; auto_merge_enabled is a separate decision from enabling tier 3. See docs/stories/US-150_tier3_governed_model.md and docs/PROD_SETUP_LOG.md (25 Sep 2026). ORIGINAL: Blocked until comparison-comparator registry, calibration dataset, governance policy, and DPO approval exist. No auto-merge policy may be inferred.</t>
         </is>
       </c>
     </row>
